--- a/debug/judgements_q_sty_swi/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Qwen3-4B-Instruct-2507/metrics_default_vs_aae.xlsx
+++ b/debug/judgements_q_sty_swi/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Qwen3-4B-Instruct-2507/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.7244094488188977</v>
+        <v>0.7054263565891473</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.7183098591549296</v>
+        <v>0.6971830985915493</v>
       </c>
       <c r="D2">
-        <v>0.303030303030303</v>
+        <v>0.3208955223880597</v>
       </c>
       <c r="E2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F2">
         <v>5</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
